--- a/annual-config.xlsx
+++ b/annual-config.xlsx
@@ -1,27 +1,40 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://blucurrent-my.sharepoint.com/personal/dpshonyak_blucurrent_org/Documents/Downloads/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="5" documentId="11_1E6278B0C8C45D5F1061036690023C0E2103FDB0" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{DE98C884-1258-475F-A744-A00B652B07A4}"/>
+  <xr:revisionPtr revIDLastSave="6" documentId="11_1E6278B0C8C45D5F1061036690023C0E2103FDB0" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{213FAB3C-DFAE-45D7-A664-3447EF21B20B}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Riders" sheetId="1" r:id="rId1"/>
     <sheet name="Schedule" sheetId="2" r:id="rId2"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="218" uniqueCount="218">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="548" uniqueCount="217">
   <si>
     <t>rider_name</t>
   </si>
@@ -411,9 +424,6 @@
   </si>
   <si>
     <t>Apr 3</t>
-  </si>
-  <si>
-    <t>Tier 4</t>
   </si>
   <si>
     <t>Ronde van Vlaanderen - Tour des Flandres</t>
@@ -1579,7 +1589,7 @@
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="B3" t="s">
         <v>7</v>
@@ -1651,7 +1661,7 @@
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="B9" t="s">
         <v>7</v>
@@ -1693,7 +1703,7 @@
         <v>8</v>
       </c>
       <c r="D12" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
@@ -1773,7 +1783,7 @@
         <v>8</v>
       </c>
       <c r="D19" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.25">
@@ -2251,7 +2261,7 @@
         <v>8</v>
       </c>
       <c r="D57" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
     </row>
     <row r="58" spans="1:5" x14ac:dyDescent="0.25">
@@ -2293,7 +2303,7 @@
         <v>35</v>
       </c>
       <c r="D60" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
     </row>
     <row r="61" spans="1:5" x14ac:dyDescent="0.25">
@@ -2363,7 +2373,7 @@
         <v>33</v>
       </c>
       <c r="D65" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="E65" t="s">
         <v>15</v>
@@ -2471,7 +2481,7 @@
         <v>14</v>
       </c>
       <c r="D71" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="E71" t="s">
         <v>15</v>
@@ -2516,13 +2526,13 @@
     </row>
     <row r="74" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="B74" t="s">
         <v>44</v>
       </c>
       <c r="C74" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="E74" t="s">
         <v>15</v>
@@ -2533,13 +2543,13 @@
     </row>
     <row r="75" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="B75" t="s">
         <v>44</v>
       </c>
       <c r="C75" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="E75" t="s">
         <v>15</v>
@@ -2550,13 +2560,13 @@
     </row>
     <row r="76" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="B76" t="s">
         <v>7</v>
       </c>
       <c r="C76" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="E76" t="s">
         <v>15</v>
@@ -2573,7 +2583,7 @@
         <v>44</v>
       </c>
       <c r="C77" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="E77" t="s">
         <v>15</v>
@@ -2584,13 +2594,13 @@
     </row>
     <row r="78" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="B78" t="s">
         <v>7</v>
       </c>
       <c r="C78" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="E78" t="s">
         <v>15</v>
@@ -2601,13 +2611,13 @@
     </row>
     <row r="79" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="B79" t="s">
         <v>7</v>
       </c>
       <c r="C79" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="E79" t="s">
         <v>15</v>
@@ -2928,7 +2938,7 @@
         <v>129</v>
       </c>
       <c r="C22" t="s">
-        <v>130</v>
+        <v>87</v>
       </c>
       <c r="D22" t="s">
         <v>91</v>
@@ -2936,10 +2946,10 @@
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
+        <v>130</v>
+      </c>
+      <c r="B23" t="s">
         <v>131</v>
-      </c>
-      <c r="B23" t="s">
-        <v>132</v>
       </c>
       <c r="C23" t="s">
         <v>116</v>
@@ -2950,10 +2960,10 @@
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
+        <v>132</v>
+      </c>
+      <c r="B24" t="s">
         <v>133</v>
-      </c>
-      <c r="B24" t="s">
-        <v>134</v>
       </c>
       <c r="C24" t="s">
         <v>101</v>
@@ -2964,10 +2974,10 @@
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
+        <v>134</v>
+      </c>
+      <c r="B25" t="s">
         <v>135</v>
-      </c>
-      <c r="B25" t="s">
-        <v>136</v>
       </c>
       <c r="C25" t="s">
         <v>87</v>
@@ -2978,10 +2988,10 @@
     </row>
     <row r="26" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
+        <v>136</v>
+      </c>
+      <c r="B26" t="s">
         <v>137</v>
-      </c>
-      <c r="B26" t="s">
-        <v>138</v>
       </c>
       <c r="C26" t="s">
         <v>116</v>
@@ -2992,10 +3002,10 @@
     </row>
     <row r="27" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
+        <v>138</v>
+      </c>
+      <c r="B27" t="s">
         <v>139</v>
-      </c>
-      <c r="B27" t="s">
-        <v>140</v>
       </c>
       <c r="C27" t="s">
         <v>87</v>
@@ -3006,10 +3016,10 @@
     </row>
     <row r="28" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
+        <v>140</v>
+      </c>
+      <c r="B28" t="s">
         <v>141</v>
-      </c>
-      <c r="B28" t="s">
-        <v>142</v>
       </c>
       <c r="C28" t="s">
         <v>101</v>
@@ -3020,10 +3030,10 @@
     </row>
     <row r="29" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
+        <v>142</v>
+      </c>
+      <c r="B29" t="s">
         <v>143</v>
-      </c>
-      <c r="B29" t="s">
-        <v>144</v>
       </c>
       <c r="C29" t="s">
         <v>87</v>
@@ -3034,10 +3044,10 @@
     </row>
     <row r="30" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
+        <v>144</v>
+      </c>
+      <c r="B30" t="s">
         <v>145</v>
-      </c>
-      <c r="B30" t="s">
-        <v>146</v>
       </c>
       <c r="C30" t="s">
         <v>101</v>
@@ -3048,10 +3058,10 @@
     </row>
     <row r="31" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
+        <v>146</v>
+      </c>
+      <c r="B31" t="s">
         <v>147</v>
-      </c>
-      <c r="B31" t="s">
-        <v>148</v>
       </c>
       <c r="C31" t="s">
         <v>116</v>
@@ -3062,10 +3072,10 @@
     </row>
     <row r="32" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
+        <v>148</v>
+      </c>
+      <c r="B32" t="s">
         <v>149</v>
-      </c>
-      <c r="B32" t="s">
-        <v>150</v>
       </c>
       <c r="C32" t="s">
         <v>87</v>
@@ -3076,10 +3086,10 @@
     </row>
     <row r="33" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
+        <v>150</v>
+      </c>
+      <c r="B33" t="s">
         <v>151</v>
-      </c>
-      <c r="B33" t="s">
-        <v>152</v>
       </c>
       <c r="C33" t="s">
         <v>101</v>
@@ -3090,24 +3100,24 @@
     </row>
     <row r="34" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
+        <v>152</v>
+      </c>
+      <c r="B34" t="s">
         <v>153</v>
-      </c>
-      <c r="B34" t="s">
-        <v>154</v>
       </c>
       <c r="C34" t="s">
         <v>116</v>
       </c>
       <c r="D34" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
     </row>
     <row r="35" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
+        <v>155</v>
+      </c>
+      <c r="B35" t="s">
         <v>156</v>
-      </c>
-      <c r="B35" t="s">
-        <v>157</v>
       </c>
       <c r="C35" t="s">
         <v>87</v>
@@ -3118,10 +3128,10 @@
     </row>
     <row r="36" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
+        <v>157</v>
+      </c>
+      <c r="B36" t="s">
         <v>158</v>
-      </c>
-      <c r="B36" t="s">
-        <v>159</v>
       </c>
       <c r="C36" t="s">
         <v>101</v>
@@ -3132,10 +3142,10 @@
     </row>
     <row r="37" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
+        <v>159</v>
+      </c>
+      <c r="B37" t="s">
         <v>160</v>
-      </c>
-      <c r="B37" t="s">
-        <v>161</v>
       </c>
       <c r="C37" t="s">
         <v>87</v>
@@ -3146,10 +3156,10 @@
     </row>
     <row r="38" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
+        <v>161</v>
+      </c>
+      <c r="B38" t="s">
         <v>162</v>
-      </c>
-      <c r="B38" t="s">
-        <v>163</v>
       </c>
       <c r="C38" t="s">
         <v>101</v>
@@ -3160,24 +3170,24 @@
     </row>
     <row r="39" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
+        <v>163</v>
+      </c>
+      <c r="B39" t="s">
         <v>164</v>
-      </c>
-      <c r="B39" t="s">
-        <v>165</v>
       </c>
       <c r="C39" t="s">
         <v>116</v>
       </c>
       <c r="D39" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
     </row>
     <row r="40" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
+        <v>165</v>
+      </c>
+      <c r="B40" t="s">
         <v>166</v>
-      </c>
-      <c r="B40" t="s">
-        <v>167</v>
       </c>
       <c r="C40" t="s">
         <v>101</v>
@@ -3188,10 +3198,10 @@
     </row>
     <row r="41" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
+        <v>167</v>
+      </c>
+      <c r="B41" t="s">
         <v>168</v>
-      </c>
-      <c r="B41" t="s">
-        <v>169</v>
       </c>
       <c r="C41" t="s">
         <v>87</v>
@@ -3202,10 +3212,10 @@
     </row>
     <row r="42" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
+        <v>169</v>
+      </c>
+      <c r="B42" t="s">
         <v>170</v>
-      </c>
-      <c r="B42" t="s">
-        <v>171</v>
       </c>
       <c r="C42" t="s">
         <v>87</v>
@@ -3216,10 +3226,10 @@
     </row>
     <row r="43" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
+        <v>171</v>
+      </c>
+      <c r="B43" t="s">
         <v>172</v>
-      </c>
-      <c r="B43" t="s">
-        <v>173</v>
       </c>
       <c r="C43" t="s">
         <v>87</v>
@@ -3230,24 +3240,24 @@
     </row>
     <row r="44" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
+        <v>173</v>
+      </c>
+      <c r="B44" t="s">
         <v>174</v>
-      </c>
-      <c r="B44" t="s">
-        <v>175</v>
       </c>
       <c r="C44" t="s">
         <v>116</v>
       </c>
       <c r="D44" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
     </row>
     <row r="45" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
+        <v>175</v>
+      </c>
+      <c r="B45" t="s">
         <v>176</v>
-      </c>
-      <c r="B45" t="s">
-        <v>177</v>
       </c>
       <c r="C45" t="s">
         <v>87</v>
@@ -3258,10 +3268,10 @@
     </row>
     <row r="46" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
+        <v>177</v>
+      </c>
+      <c r="B46" t="s">
         <v>178</v>
-      </c>
-      <c r="B46" t="s">
-        <v>179</v>
       </c>
       <c r="C46" t="s">
         <v>101</v>
@@ -3272,10 +3282,10 @@
     </row>
     <row r="47" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
+        <v>179</v>
+      </c>
+      <c r="B47" t="s">
         <v>180</v>
-      </c>
-      <c r="B47" t="s">
-        <v>181</v>
       </c>
       <c r="C47" t="s">
         <v>87</v>
@@ -3286,10 +3296,10 @@
     </row>
     <row r="48" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
+        <v>181</v>
+      </c>
+      <c r="B48" t="s">
         <v>182</v>
-      </c>
-      <c r="B48" t="s">
-        <v>183</v>
       </c>
       <c r="C48" t="s">
         <v>101</v>
@@ -3300,10 +3310,10 @@
     </row>
     <row r="49" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
+        <v>183</v>
+      </c>
+      <c r="B49" t="s">
         <v>184</v>
-      </c>
-      <c r="B49" t="s">
-        <v>185</v>
       </c>
       <c r="C49" t="s">
         <v>101</v>
@@ -3314,10 +3324,10 @@
     </row>
     <row r="50" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
+        <v>185</v>
+      </c>
+      <c r="B50" t="s">
         <v>186</v>
-      </c>
-      <c r="B50" t="s">
-        <v>187</v>
       </c>
       <c r="C50" t="s">
         <v>87</v>
@@ -3328,10 +3338,10 @@
     </row>
     <row r="51" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
+        <v>187</v>
+      </c>
+      <c r="B51" t="s">
         <v>188</v>
-      </c>
-      <c r="B51" t="s">
-        <v>189</v>
       </c>
       <c r="C51" t="s">
         <v>87</v>
@@ -3342,38 +3352,38 @@
     </row>
     <row r="52" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
+        <v>189</v>
+      </c>
+      <c r="B52" t="s">
         <v>190</v>
-      </c>
-      <c r="B52" t="s">
-        <v>191</v>
       </c>
       <c r="C52" t="s">
         <v>116</v>
       </c>
       <c r="D52" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
     </row>
     <row r="53" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
+        <v>192</v>
+      </c>
+      <c r="B53" t="s">
         <v>193</v>
-      </c>
-      <c r="B53" t="s">
-        <v>194</v>
       </c>
       <c r="C53" t="s">
         <v>116</v>
       </c>
       <c r="D53" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
     </row>
     <row r="54" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
+        <v>194</v>
+      </c>
+      <c r="B54" t="s">
         <v>195</v>
-      </c>
-      <c r="B54" t="s">
-        <v>196</v>
       </c>
       <c r="C54" t="s">
         <v>87</v>
@@ -3384,10 +3394,10 @@
     </row>
     <row r="55" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="B55" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="C55" t="s">
         <v>87</v>
@@ -3398,24 +3408,24 @@
     </row>
     <row r="56" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
+        <v>197</v>
+      </c>
+      <c r="B56" t="s">
         <v>198</v>
-      </c>
-      <c r="B56" t="s">
-        <v>199</v>
       </c>
       <c r="C56" t="s">
         <v>101</v>
       </c>
       <c r="D56" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
     </row>
     <row r="57" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
+        <v>199</v>
+      </c>
+      <c r="B57" t="s">
         <v>200</v>
-      </c>
-      <c r="B57" t="s">
-        <v>201</v>
       </c>
       <c r="C57" t="s">
         <v>87</v>
@@ -3426,10 +3436,10 @@
     </row>
     <row r="58" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
+        <v>201</v>
+      </c>
+      <c r="B58" t="s">
         <v>202</v>
-      </c>
-      <c r="B58" t="s">
-        <v>203</v>
       </c>
       <c r="C58" t="s">
         <v>87</v>
@@ -3440,10 +3450,10 @@
     </row>
     <row r="59" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
+        <v>203</v>
+      </c>
+      <c r="B59" t="s">
         <v>204</v>
-      </c>
-      <c r="B59" t="s">
-        <v>205</v>
       </c>
       <c r="C59" t="s">
         <v>116</v>
@@ -3454,10 +3464,10 @@
     </row>
     <row r="60" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
+        <v>205</v>
+      </c>
+      <c r="B60" t="s">
         <v>206</v>
-      </c>
-      <c r="B60" t="s">
-        <v>207</v>
       </c>
       <c r="C60" t="s">
         <v>87</v>
@@ -3468,10 +3478,10 @@
     </row>
     <row r="61" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
+        <v>207</v>
+      </c>
+      <c r="B61" t="s">
         <v>208</v>
-      </c>
-      <c r="B61" t="s">
-        <v>209</v>
       </c>
       <c r="C61" t="s">
         <v>87</v>

--- a/annual-config.xlsx
+++ b/annual-config.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://blucurrent-my.sharepoint.com/personal/dpshonyak_blucurrent_org/Documents/Downloads/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="6" documentId="11_1E6278B0C8C45D5F1061036690023C0E2103FDB0" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{213FAB3C-DFAE-45D7-A664-3447EF21B20B}"/>
+  <xr:revisionPtr revIDLastSave="15" documentId="11_1E6278B0C8C45D5F1061036690023C0E2103FDB0" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{044EB6F2-8957-45AC-A26B-52F5F4774712}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-60" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Riders" sheetId="1" r:id="rId1"/>
@@ -594,9 +594,6 @@
     <t>Gran Premio città di Peccioli - Coppa Sabatini</t>
   </si>
   <si>
-    <t>Sep 17</t>
-  </si>
-  <si>
     <t>SUPER 8 Classic</t>
   </si>
   <si>
@@ -685,6 +682,9 @@
   </si>
   <si>
     <t>Bryan Coquard</t>
+  </si>
+  <si>
+    <t>Sep 10</t>
   </si>
 </sst>
 </file>
@@ -1168,8 +1168,9 @@
     <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="42">
     <cellStyle name="20% - Accent1" xfId="19" builtinId="30" customBuiltin="1"/>
@@ -1589,7 +1590,7 @@
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="B3" t="s">
         <v>7</v>
@@ -1661,7 +1662,7 @@
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="B9" t="s">
         <v>7</v>
@@ -1703,7 +1704,7 @@
         <v>8</v>
       </c>
       <c r="D12" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
@@ -1783,7 +1784,7 @@
         <v>8</v>
       </c>
       <c r="D19" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.25">
@@ -2261,7 +2262,7 @@
         <v>8</v>
       </c>
       <c r="D57" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
     </row>
     <row r="58" spans="1:5" x14ac:dyDescent="0.25">
@@ -2303,7 +2304,7 @@
         <v>35</v>
       </c>
       <c r="D60" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
     </row>
     <row r="61" spans="1:5" x14ac:dyDescent="0.25">
@@ -2373,7 +2374,7 @@
         <v>33</v>
       </c>
       <c r="D65" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="E65" t="s">
         <v>15</v>
@@ -2481,7 +2482,7 @@
         <v>14</v>
       </c>
       <c r="D71" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="E71" t="s">
         <v>15</v>
@@ -2526,13 +2527,13 @@
     </row>
     <row r="74" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="B74" t="s">
         <v>44</v>
       </c>
       <c r="C74" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="E74" t="s">
         <v>15</v>
@@ -2543,13 +2544,13 @@
     </row>
     <row r="75" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="B75" t="s">
         <v>44</v>
       </c>
       <c r="C75" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="E75" t="s">
         <v>15</v>
@@ -2560,13 +2561,13 @@
     </row>
     <row r="76" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="B76" t="s">
         <v>7</v>
       </c>
       <c r="C76" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="E76" t="s">
         <v>15</v>
@@ -2583,7 +2584,7 @@
         <v>44</v>
       </c>
       <c r="C77" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="E77" t="s">
         <v>15</v>
@@ -2594,13 +2595,13 @@
     </row>
     <row r="78" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="B78" t="s">
         <v>7</v>
       </c>
       <c r="C78" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="E78" t="s">
         <v>15</v>
@@ -2611,13 +2612,13 @@
     </row>
     <row r="79" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="B79" t="s">
         <v>7</v>
       </c>
       <c r="C79" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="E79" t="s">
         <v>15</v>
@@ -2635,6 +2636,12 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:D61"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="46" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="14.5703125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="5.7109375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="23.7109375" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
@@ -3240,30 +3247,30 @@
     </row>
     <row r="44" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="B44" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="C44" t="s">
-        <v>116</v>
+        <v>87</v>
       </c>
       <c r="D44" t="s">
-        <v>154</v>
+        <v>88</v>
       </c>
     </row>
     <row r="45" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="B45" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="C45" t="s">
-        <v>87</v>
+        <v>116</v>
       </c>
       <c r="D45" t="s">
-        <v>88</v>
+        <v>154</v>
       </c>
     </row>
     <row r="46" spans="1:4" x14ac:dyDescent="0.25">
@@ -3296,13 +3303,13 @@
     </row>
     <row r="48" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
-        <v>181</v>
-      </c>
-      <c r="B48" t="s">
-        <v>182</v>
+        <v>185</v>
+      </c>
+      <c r="B48" s="1" t="s">
+        <v>216</v>
       </c>
       <c r="C48" t="s">
-        <v>101</v>
+        <v>87</v>
       </c>
       <c r="D48" t="s">
         <v>91</v>
@@ -3310,10 +3317,10 @@
     </row>
     <row r="49" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="B49" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="C49" t="s">
         <v>101</v>
@@ -3324,13 +3331,13 @@
     </row>
     <row r="50" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="B50" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="C50" t="s">
-        <v>87</v>
+        <v>101</v>
       </c>
       <c r="D50" t="s">
         <v>91</v>
@@ -3338,10 +3345,10 @@
     </row>
     <row r="51" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
+        <v>186</v>
+      </c>
+      <c r="B51" t="s">
         <v>187</v>
-      </c>
-      <c r="B51" t="s">
-        <v>188</v>
       </c>
       <c r="C51" t="s">
         <v>87</v>
@@ -3352,38 +3359,38 @@
     </row>
     <row r="52" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
+        <v>188</v>
+      </c>
+      <c r="B52" t="s">
         <v>189</v>
-      </c>
-      <c r="B52" t="s">
-        <v>190</v>
       </c>
       <c r="C52" t="s">
         <v>116</v>
       </c>
       <c r="D52" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
     </row>
     <row r="53" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
+        <v>191</v>
+      </c>
+      <c r="B53" t="s">
         <v>192</v>
-      </c>
-      <c r="B53" t="s">
-        <v>193</v>
       </c>
       <c r="C53" t="s">
         <v>116</v>
       </c>
       <c r="D53" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
     </row>
     <row r="54" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
+        <v>193</v>
+      </c>
+      <c r="B54" t="s">
         <v>194</v>
-      </c>
-      <c r="B54" t="s">
-        <v>195</v>
       </c>
       <c r="C54" t="s">
         <v>87</v>
@@ -3394,10 +3401,10 @@
     </row>
     <row r="55" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="B55" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="C55" t="s">
         <v>87</v>
@@ -3408,24 +3415,24 @@
     </row>
     <row r="56" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
+        <v>196</v>
+      </c>
+      <c r="B56" t="s">
         <v>197</v>
-      </c>
-      <c r="B56" t="s">
-        <v>198</v>
       </c>
       <c r="C56" t="s">
         <v>101</v>
       </c>
       <c r="D56" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
     </row>
     <row r="57" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
+        <v>198</v>
+      </c>
+      <c r="B57" t="s">
         <v>199</v>
-      </c>
-      <c r="B57" t="s">
-        <v>200</v>
       </c>
       <c r="C57" t="s">
         <v>87</v>
@@ -3436,10 +3443,10 @@
     </row>
     <row r="58" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
+        <v>200</v>
+      </c>
+      <c r="B58" t="s">
         <v>201</v>
-      </c>
-      <c r="B58" t="s">
-        <v>202</v>
       </c>
       <c r="C58" t="s">
         <v>87</v>
@@ -3450,10 +3457,10 @@
     </row>
     <row r="59" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
+        <v>202</v>
+      </c>
+      <c r="B59" t="s">
         <v>203</v>
-      </c>
-      <c r="B59" t="s">
-        <v>204</v>
       </c>
       <c r="C59" t="s">
         <v>116</v>
@@ -3464,10 +3471,10 @@
     </row>
     <row r="60" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
+        <v>204</v>
+      </c>
+      <c r="B60" t="s">
         <v>205</v>
-      </c>
-      <c r="B60" t="s">
-        <v>206</v>
       </c>
       <c r="C60" t="s">
         <v>87</v>
@@ -3478,10 +3485,10 @@
     </row>
     <row r="61" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
+        <v>206</v>
+      </c>
+      <c r="B61" t="s">
         <v>207</v>
-      </c>
-      <c r="B61" t="s">
-        <v>208</v>
       </c>
       <c r="C61" t="s">
         <v>87</v>

--- a/annual-config.xlsx
+++ b/annual-config.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://blucurrent-my.sharepoint.com/personal/dpshonyak_blucurrent_org/Documents/Downloads/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="15" documentId="11_1E6278B0C8C45D5F1061036690023C0E2103FDB0" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{044EB6F2-8957-45AC-A26B-52F5F4774712}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{94D4F3A6-2B1B-4094-846B-0826E69963A2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-60" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -594,9 +594,6 @@
     <t>Gran Premio città di Peccioli - Coppa Sabatini</t>
   </si>
   <si>
-    <t>SUPER 8 Classic</t>
-  </si>
-  <si>
     <t>Sep 19</t>
   </si>
   <si>
@@ -685,6 +682,9 @@
   </si>
   <si>
     <t>Sep 10</t>
+  </si>
+  <si>
+    <t>Flandrien 0.0 Classic</t>
   </si>
 </sst>
 </file>
@@ -1590,7 +1590,7 @@
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="B3" t="s">
         <v>7</v>
@@ -1662,7 +1662,7 @@
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="B9" t="s">
         <v>7</v>
@@ -1704,7 +1704,7 @@
         <v>8</v>
       </c>
       <c r="D12" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
@@ -1784,7 +1784,7 @@
         <v>8</v>
       </c>
       <c r="D19" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.25">
@@ -2262,7 +2262,7 @@
         <v>8</v>
       </c>
       <c r="D57" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
     </row>
     <row r="58" spans="1:5" x14ac:dyDescent="0.25">
@@ -2304,7 +2304,7 @@
         <v>35</v>
       </c>
       <c r="D60" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
     </row>
     <row r="61" spans="1:5" x14ac:dyDescent="0.25">
@@ -2374,7 +2374,7 @@
         <v>33</v>
       </c>
       <c r="D65" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="E65" t="s">
         <v>15</v>
@@ -2482,7 +2482,7 @@
         <v>14</v>
       </c>
       <c r="D71" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="E71" t="s">
         <v>15</v>
@@ -2527,13 +2527,13 @@
     </row>
     <row r="74" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="B74" t="s">
         <v>44</v>
       </c>
       <c r="C74" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="E74" t="s">
         <v>15</v>
@@ -2544,13 +2544,13 @@
     </row>
     <row r="75" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="B75" t="s">
         <v>44</v>
       </c>
       <c r="C75" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="E75" t="s">
         <v>15</v>
@@ -2561,13 +2561,13 @@
     </row>
     <row r="76" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="B76" t="s">
         <v>7</v>
       </c>
       <c r="C76" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="E76" t="s">
         <v>15</v>
@@ -2584,7 +2584,7 @@
         <v>44</v>
       </c>
       <c r="C77" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="E77" t="s">
         <v>15</v>
@@ -2595,13 +2595,13 @@
     </row>
     <row r="78" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="B78" t="s">
         <v>7</v>
       </c>
       <c r="C78" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="E78" t="s">
         <v>15</v>
@@ -2612,13 +2612,13 @@
     </row>
     <row r="79" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="B79" t="s">
         <v>7</v>
       </c>
       <c r="C79" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="E79" t="s">
         <v>15</v>
@@ -3306,7 +3306,7 @@
         <v>185</v>
       </c>
       <c r="B48" s="1" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="C48" t="s">
         <v>87</v>
@@ -3345,10 +3345,10 @@
     </row>
     <row r="51" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
+        <v>216</v>
+      </c>
+      <c r="B51" t="s">
         <v>186</v>
-      </c>
-      <c r="B51" t="s">
-        <v>187</v>
       </c>
       <c r="C51" t="s">
         <v>87</v>
@@ -3359,38 +3359,38 @@
     </row>
     <row r="52" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
+        <v>187</v>
+      </c>
+      <c r="B52" t="s">
         <v>188</v>
-      </c>
-      <c r="B52" t="s">
-        <v>189</v>
       </c>
       <c r="C52" t="s">
         <v>116</v>
       </c>
       <c r="D52" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
     </row>
     <row r="53" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
+        <v>190</v>
+      </c>
+      <c r="B53" t="s">
         <v>191</v>
-      </c>
-      <c r="B53" t="s">
-        <v>192</v>
       </c>
       <c r="C53" t="s">
         <v>116</v>
       </c>
       <c r="D53" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
     </row>
     <row r="54" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
+        <v>192</v>
+      </c>
+      <c r="B54" t="s">
         <v>193</v>
-      </c>
-      <c r="B54" t="s">
-        <v>194</v>
       </c>
       <c r="C54" t="s">
         <v>87</v>
@@ -3401,10 +3401,10 @@
     </row>
     <row r="55" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="B55" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="C55" t="s">
         <v>87</v>
@@ -3415,24 +3415,24 @@
     </row>
     <row r="56" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
+        <v>195</v>
+      </c>
+      <c r="B56" t="s">
         <v>196</v>
-      </c>
-      <c r="B56" t="s">
-        <v>197</v>
       </c>
       <c r="C56" t="s">
         <v>101</v>
       </c>
       <c r="D56" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
     </row>
     <row r="57" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
+        <v>197</v>
+      </c>
+      <c r="B57" t="s">
         <v>198</v>
-      </c>
-      <c r="B57" t="s">
-        <v>199</v>
       </c>
       <c r="C57" t="s">
         <v>87</v>
@@ -3443,10 +3443,10 @@
     </row>
     <row r="58" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
+        <v>199</v>
+      </c>
+      <c r="B58" t="s">
         <v>200</v>
-      </c>
-      <c r="B58" t="s">
-        <v>201</v>
       </c>
       <c r="C58" t="s">
         <v>87</v>
@@ -3457,10 +3457,10 @@
     </row>
     <row r="59" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
+        <v>201</v>
+      </c>
+      <c r="B59" t="s">
         <v>202</v>
-      </c>
-      <c r="B59" t="s">
-        <v>203</v>
       </c>
       <c r="C59" t="s">
         <v>116</v>
@@ -3471,10 +3471,10 @@
     </row>
     <row r="60" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
+        <v>203</v>
+      </c>
+      <c r="B60" t="s">
         <v>204</v>
-      </c>
-      <c r="B60" t="s">
-        <v>205</v>
       </c>
       <c r="C60" t="s">
         <v>87</v>
@@ -3485,10 +3485,10 @@
     </row>
     <row r="61" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
+        <v>205</v>
+      </c>
+      <c r="B61" t="s">
         <v>206</v>
-      </c>
-      <c r="B61" t="s">
-        <v>207</v>
       </c>
       <c r="C61" t="s">
         <v>87</v>
@@ -3499,6 +3499,7 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
 </worksheet>
 </file>
 
